--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R86db31e021d94b2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Re86f33765273486a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6ce1a457519d4352"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R42ee59f0071f4621"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6ce1a457519d4352"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R42ee59f0071f4621"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6d54351cf95342be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R5f067775aced4620"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6d54351cf95342be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R5f067775aced4620"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R80b5a397e8f84d3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Re1b9bbcf480d42e5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R80b5a397e8f84d3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Re1b9bbcf480d42e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1daf9845269440df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rf7045a0613024dd3"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1daf9845269440df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rf7045a0613024dd3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R933e1e0b91174c29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rfca4d244d0fc4e3a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R933e1e0b91174c29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rfca4d244d0fc4e3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc163d0cb75cb4c4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rc86670a597ac45d6"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc163d0cb75cb4c4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rc86670a597ac45d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra2a62ffc62ab4df1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R044fe276f13b4a68"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra2a62ffc62ab4df1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R044fe276f13b4a68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0a40962550d44842"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R462cb524100c4b5b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0a40962550d44842"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R462cb524100c4b5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb34ed54ca21c4fe0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R18db5a5922404ed4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb34ed54ca21c4fe0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R18db5a5922404ed4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd432ee98ea2c4ea1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R4ddd592d9a9949ad"/>
   </x:sheets>
 </x:workbook>
 </file>
